--- a/filesystem/MarketingOps/Reporting/Q1_2026_managed_spend_export.xlsx
+++ b/filesystem/MarketingOps/Reporting/Q1_2026_managed_spend_export.xlsx
@@ -176,7 +176,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -324,11 +324,90 @@
         <color rgb="000F172A"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <bottom/>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <right/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -446,6 +525,21 @@
     </xf>
     <xf numFmtId="164" fontId="17" fillId="5" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -772,12 +866,6 @@
           <t>THORNFIELD LIFE SCIENCES MARKETING — Q1 2026 Managed Spend Export (Platform-Level, by Client)</t>
         </is>
       </c>
-      <c r="B1" s="15" t="n"/>
-      <c r="C1" s="15" t="n"/>
-      <c r="D1" s="15" t="n"/>
-      <c r="E1" s="15" t="n"/>
-      <c r="F1" s="15" t="n"/>
-      <c r="G1" s="15" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="16" t="inlineStr">
@@ -785,16 +873,16 @@
           <t>Prepared by:</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="50" t="inlineStr">
         <is>
           <t>Grace Feldman, Director, Analytics &amp; Reporting</t>
         </is>
       </c>
-      <c r="C2" s="17" t="n"/>
-      <c r="D2" s="17" t="n"/>
-      <c r="E2" s="17" t="n"/>
-      <c r="F2" s="17" t="n"/>
-      <c r="G2" s="18" t="n"/>
+      <c r="C2" s="44" t="n"/>
+      <c r="D2" s="44" t="n"/>
+      <c r="E2" s="44" t="n"/>
+      <c r="F2" s="44" t="n"/>
+      <c r="G2" s="45" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
       <c r="A3" s="19" t="inlineStr">
@@ -802,16 +890,12 @@
           <t>Source:</t>
         </is>
       </c>
-      <c r="B3" s="20" t="inlineStr">
+      <c r="B3" s="51" t="inlineStr">
         <is>
           <t>ERPNext (erp.thornfieldlsm.com) — Customer master joined to Sales Order line items, aggregated by billing month</t>
         </is>
       </c>
-      <c r="C3" s="20" t="n"/>
-      <c r="D3" s="20" t="n"/>
-      <c r="E3" s="20" t="n"/>
-      <c r="F3" s="20" t="n"/>
-      <c r="G3" s="21" t="n"/>
+      <c r="G3" s="46" t="n"/>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="19" t="inlineStr">
@@ -819,16 +903,12 @@
           <t>Reporting basis:</t>
         </is>
       </c>
-      <c r="B4" s="20" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>Gross platform spend managed by Thornfield on behalf of client during the quarter (excludes management fee, reserve, and pass-through creative production).</t>
         </is>
       </c>
-      <c r="C4" s="20" t="n"/>
-      <c r="D4" s="20" t="n"/>
-      <c r="E4" s="20" t="n"/>
-      <c r="F4" s="20" t="n"/>
-      <c r="G4" s="21" t="n"/>
+      <c r="G4" s="46" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
@@ -836,16 +916,12 @@
           <t>Data as of:</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="51" t="inlineStr">
         <is>
           <t>01/12/2026</t>
         </is>
       </c>
-      <c r="C5" s="20" t="n"/>
-      <c r="D5" s="20" t="n"/>
-      <c r="E5" s="20" t="n"/>
-      <c r="F5" s="20" t="n"/>
-      <c r="G5" s="21" t="n"/>
+      <c r="G5" s="46" t="n"/>
     </row>
     <row r="6" ht="32" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
@@ -853,16 +929,12 @@
           <t>Status:</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="51" t="inlineStr">
         <is>
           <t>Q1 2026 in progress — data current as of anchor date 01/12/2026. January partial (billing days 1–12 only); February and March not yet in period.</t>
         </is>
       </c>
-      <c r="C6" s="20" t="n"/>
-      <c r="D6" s="20" t="n"/>
-      <c r="E6" s="20" t="n"/>
-      <c r="F6" s="20" t="n"/>
-      <c r="G6" s="21" t="n"/>
+      <c r="G6" s="46" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="22" t="inlineStr">
@@ -870,16 +942,16 @@
           <t>Currency:</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>USD, format $#,##0</t>
         </is>
       </c>
-      <c r="C7" s="23" t="n"/>
-      <c r="D7" s="23" t="n"/>
-      <c r="E7" s="23" t="n"/>
-      <c r="F7" s="23" t="n"/>
-      <c r="G7" s="24" t="n"/>
+      <c r="C7" s="47" t="n"/>
+      <c r="D7" s="47" t="n"/>
+      <c r="E7" s="47" t="n"/>
+      <c r="F7" s="47" t="n"/>
+      <c r="G7" s="48" t="n"/>
     </row>
     <row r="8" ht="14" customHeight="1"/>
     <row r="9" ht="32" customHeight="1">
@@ -2263,7 +2335,7 @@
       </c>
       <c r="C53" s="36" t="inlineStr">
         <is>
-          <t>Inherited — Bramwell</t>
+          <t>Thornfield native</t>
         </is>
       </c>
       <c r="D53" s="34" t="inlineStr">
@@ -2296,7 +2368,7 @@
       </c>
       <c r="C54" s="30" t="inlineStr">
         <is>
-          <t>Inherited — Bramwell</t>
+          <t>Thornfield native</t>
         </is>
       </c>
       <c r="D54" s="28" t="inlineStr">
@@ -2362,7 +2434,7 @@
       </c>
       <c r="C56" s="30" t="inlineStr">
         <is>
-          <t>Inherited — Bramwell</t>
+          <t>Thornfield native</t>
         </is>
       </c>
       <c r="D56" s="28" t="inlineStr">
@@ -2395,7 +2467,7 @@
       </c>
       <c r="C57" s="36" t="inlineStr">
         <is>
-          <t>Inherited — Bramwell</t>
+          <t>Thornfield native</t>
         </is>
       </c>
       <c r="D57" s="34" t="inlineStr">
@@ -2428,7 +2500,7 @@
       </c>
       <c r="C58" s="30" t="inlineStr">
         <is>
-          <t>Inherited — Bramwell</t>
+          <t>Thornfield native</t>
         </is>
       </c>
       <c r="D58" s="28" t="inlineStr">
@@ -2562,33 +2634,35 @@
       <c r="G63" s="40" t="n"/>
     </row>
     <row r="64" ht="24" customHeight="1">
-      <c r="A64" s="41" t="inlineStr">
+      <c r="A64" s="52" t="inlineStr">
         <is>
           <t>VENDOR-MTAN</t>
         </is>
       </c>
-      <c r="B64" s="41" t="n"/>
-      <c r="C64" s="41" t="n"/>
-      <c r="D64" s="41" t="n"/>
-      <c r="E64" s="41" t="n"/>
-      <c r="F64" s="41" t="n"/>
-      <c r="G64" s="41" t="n"/>
+      <c r="B64" s="49" t="n"/>
+      <c r="C64" s="49" t="n"/>
+      <c r="D64" s="49" t="n"/>
+      <c r="E64" s="49" t="n"/>
+      <c r="F64" s="49" t="n"/>
+      <c r="G64" s="49" t="n"/>
     </row>
     <row r="65" ht="16" customHeight="1"/>
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="42" t="inlineStr">
         <is>
-          <t>TOTALS (53 client rows + 1 vendor placement memo)</t>
+          <t>TOTALS (52 client rows + 1 vendor placement memo)</t>
         </is>
       </c>
       <c r="B66" s="42" t="n"/>
       <c r="C66" s="42" t="n"/>
       <c r="D66" s="42" t="n"/>
-      <c r="E66" s="43" t="n">
-        <v>954300</v>
-      </c>
-      <c r="F66" s="43" t="n">
-        <v>954300</v>
+      <c r="E66" s="43">
+        <f>SUM(E10:E61)</f>
+        <v>930800</v>
+      </c>
+      <c r="F66" s="43">
+        <f>SUM(F10:F61)</f>
+        <v>930800</v>
       </c>
       <c r="G66" s="42" t="inlineStr"/>
     </row>

--- a/filesystem/MarketingOps/Reporting/Q1_2026_managed_spend_export.xlsx
+++ b/filesystem/MarketingOps/Reporting/Q1_2026_managed_spend_export.xlsx
@@ -1245,7 +1245,7 @@
       </c>
       <c r="D18" s="28" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E18" s="31" t="n">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="D50" s="28" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E50" s="31" t="n">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E51" s="37" t="n">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="D53" s="34" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E53" s="37" t="n">

--- a/filesystem/MarketingOps/Reporting/Q1_2026_managed_spend_export.xlsx
+++ b/filesystem/MarketingOps/Reporting/Q1_2026_managed_spend_export.xlsx
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G53" s="39" t="inlineStr">
         <is>
-          <t>inherited account</t>
+          <t>Thornfield-native account</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="G54" s="33" t="inlineStr">
         <is>
-          <t>inherited account; regulated client</t>
+          <t>Thornfield-native account; regulated client</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="G56" s="33" t="inlineStr">
         <is>
-          <t>inherited account; regulated client</t>
+          <t>Thornfield-native account; regulated client</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="G57" s="39" t="inlineStr">
         <is>
-          <t>inherited account</t>
+          <t>Thornfield-native account</t>
         </is>
       </c>
     </row>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="G58" s="33" t="inlineStr">
         <is>
-          <t>inherited account; regulated client</t>
+          <t>Thornfield-native account; regulated client</t>
         </is>
       </c>
     </row>

--- a/filesystem/MarketingOps/Reporting/Q1_2026_managed_spend_export.xlsx
+++ b/filesystem/MarketingOps/Reporting/Q1_2026_managed_spend_export.xlsx
@@ -931,7 +931,7 @@
       </c>
       <c r="B6" s="51" t="inlineStr">
         <is>
-          <t>Q1 2026 in progress — data current as of anchor date 01/12/2026. January partial (billing days 1–12 only); February and March not yet in period.</t>
+          <t>Q1 2026 in progress. January partial (billing days 1–12 only); February and March not yet in period.</t>
         </is>
       </c>
       <c r="G6" s="46" t="n"/>

--- a/filesystem/MarketingOps/Reporting/Q1_2026_managed_spend_export.xlsx
+++ b/filesystem/MarketingOps/Reporting/Q1_2026_managed_spend_export.xlsx
@@ -1028,7 +1028,7 @@
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Meridian Biosystems</t>
+          <t>Thistlewood Biosystems</t>
         </is>
       </c>
       <c r="C11" s="36" t="inlineStr">

--- a/filesystem/MarketingOps/Reporting/Q1_2026_managed_spend_export.xlsx
+++ b/filesystem/MarketingOps/Reporting/Q1_2026_managed_spend_export.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -124,6 +124,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="FF475569"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="9">
@@ -407,7 +413,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -540,6 +546,12 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1134,7 +1146,7 @@
       <c r="F14" s="32" t="n">
         <v>9200</v>
       </c>
-      <c r="G14" s="33" t="inlineStr">
+      <c r="G14" s="53" t="inlineStr">
         <is>
           <t>regulated client</t>
         </is>
@@ -1312,7 +1324,7 @@
       <c r="F20" s="32" t="n">
         <v>14800</v>
       </c>
-      <c r="G20" s="33" t="inlineStr">
+      <c r="G20" s="53" t="inlineStr">
         <is>
           <t>regulated client</t>
         </is>
@@ -1403,7 +1415,7 @@
       <c r="F23" s="38" t="n">
         <v>18400</v>
       </c>
-      <c r="G23" s="39" t="inlineStr">
+      <c r="G23" s="54" t="inlineStr">
         <is>
           <t>regulated client</t>
         </is>
@@ -1465,7 +1477,7 @@
       <c r="F25" s="38" t="n">
         <v>23500</v>
       </c>
-      <c r="G25" s="39" t="inlineStr">
+      <c r="G25" s="54" t="inlineStr">
         <is>
           <t>regulated client</t>
         </is>
@@ -1527,7 +1539,7 @@
       <c r="F27" s="38" t="n">
         <v>34700</v>
       </c>
-      <c r="G27" s="39" t="inlineStr">
+      <c r="G27" s="54" t="inlineStr">
         <is>
           <t>regulated client</t>
         </is>
@@ -1560,7 +1572,7 @@
       <c r="F28" s="32" t="n">
         <v>5600</v>
       </c>
-      <c r="G28" s="33" t="inlineStr">
+      <c r="G28" s="53" t="inlineStr">
         <is>
           <t>regulated client</t>
         </is>
@@ -1651,7 +1663,7 @@
       <c r="F31" s="38" t="n">
         <v>16500</v>
       </c>
-      <c r="G31" s="39" t="inlineStr">
+      <c r="G31" s="54" t="inlineStr">
         <is>
           <t>regulated client</t>
         </is>
@@ -1829,7 +1841,7 @@
       <c r="F37" s="38" t="n">
         <v>11100</v>
       </c>
-      <c r="G37" s="39" t="inlineStr">
+      <c r="G37" s="54" t="inlineStr">
         <is>
           <t>regulated client</t>
         </is>
@@ -1920,7 +1932,7 @@
       <c r="F40" s="32" t="n">
         <v>9000</v>
       </c>
-      <c r="G40" s="33" t="inlineStr">
+      <c r="G40" s="53" t="inlineStr">
         <is>
           <t>inherited account</t>
         </is>
@@ -1953,7 +1965,7 @@
       <c r="F41" s="38" t="n">
         <v>22800</v>
       </c>
-      <c r="G41" s="39" t="inlineStr">
+      <c r="G41" s="54" t="inlineStr">
         <is>
           <t>inherited account; regulated client</t>
         </is>
@@ -1986,7 +1998,7 @@
       <c r="F42" s="32" t="n">
         <v>13800</v>
       </c>
-      <c r="G42" s="33" t="inlineStr">
+      <c r="G42" s="53" t="inlineStr">
         <is>
           <t>inherited account</t>
         </is>
@@ -2019,7 +2031,7 @@
       <c r="F43" s="38" t="n">
         <v>31500</v>
       </c>
-      <c r="G43" s="39" t="inlineStr">
+      <c r="G43" s="54" t="inlineStr">
         <is>
           <t>inherited account</t>
         </is>
@@ -2052,7 +2064,7 @@
       <c r="F44" s="32" t="n">
         <v>6400</v>
       </c>
-      <c r="G44" s="33" t="inlineStr">
+      <c r="G44" s="53" t="inlineStr">
         <is>
           <t>inherited account</t>
         </is>
@@ -2085,7 +2097,7 @@
       <c r="F45" s="38" t="n">
         <v>16400</v>
       </c>
-      <c r="G45" s="39" t="inlineStr">
+      <c r="G45" s="54" t="inlineStr">
         <is>
           <t>inherited account</t>
         </is>
@@ -2118,7 +2130,7 @@
       <c r="F46" s="32" t="n">
         <v>27500</v>
       </c>
-      <c r="G46" s="33" t="inlineStr">
+      <c r="G46" s="53" t="inlineStr">
         <is>
           <t>inherited account; regulated client</t>
         </is>
@@ -2151,7 +2163,7 @@
       <c r="F47" s="38" t="n">
         <v>32800</v>
       </c>
-      <c r="G47" s="39" t="inlineStr">
+      <c r="G47" s="54" t="inlineStr">
         <is>
           <t>inherited account; on legacy-accounts renewal rate</t>
         </is>
@@ -2184,7 +2196,7 @@
       <c r="F48" s="32" t="n">
         <v>11200</v>
       </c>
-      <c r="G48" s="33" t="inlineStr">
+      <c r="G48" s="53" t="inlineStr">
         <is>
           <t>inherited account</t>
         </is>
@@ -2217,7 +2229,7 @@
       <c r="F49" s="38" t="n">
         <v>19000</v>
       </c>
-      <c r="G49" s="39" t="inlineStr">
+      <c r="G49" s="54" t="inlineStr">
         <is>
           <t>inherited account; regulated client</t>
         </is>
@@ -2250,7 +2262,7 @@
       <c r="F50" s="32" t="n">
         <v>21800</v>
       </c>
-      <c r="G50" s="33" t="inlineStr">
+      <c r="G50" s="53" t="inlineStr">
         <is>
           <t>inherited account</t>
         </is>
@@ -2283,7 +2295,7 @@
       <c r="F51" s="38" t="n">
         <v>32000</v>
       </c>
-      <c r="G51" s="39" t="inlineStr">
+      <c r="G51" s="54" t="inlineStr">
         <is>
           <t>inherited account</t>
         </is>
@@ -2316,7 +2328,7 @@
       <c r="F52" s="32" t="n">
         <v>8800</v>
       </c>
-      <c r="G52" s="33" t="inlineStr">
+      <c r="G52" s="53" t="inlineStr">
         <is>
           <t>inherited account; regulated client</t>
         </is>
@@ -2349,7 +2361,7 @@
       <c r="F53" s="38" t="n">
         <v>14700</v>
       </c>
-      <c r="G53" s="39" t="inlineStr">
+      <c r="G53" s="54" t="inlineStr">
         <is>
           <t>Thornfield-native account</t>
         </is>
@@ -2382,7 +2394,7 @@
       <c r="F54" s="32" t="n">
         <v>24500</v>
       </c>
-      <c r="G54" s="33" t="inlineStr">
+      <c r="G54" s="53" t="inlineStr">
         <is>
           <t>Thornfield-native account; regulated client</t>
         </is>
@@ -2415,7 +2427,7 @@
       <c r="F55" s="38" t="n">
         <v>10700</v>
       </c>
-      <c r="G55" s="39" t="inlineStr">
+      <c r="G55" s="54" t="inlineStr">
         <is>
           <t>inherited account</t>
         </is>
@@ -2448,7 +2460,7 @@
       <c r="F56" s="32" t="n">
         <v>37600</v>
       </c>
-      <c r="G56" s="33" t="inlineStr">
+      <c r="G56" s="53" t="inlineStr">
         <is>
           <t>Thornfield-native account; regulated client</t>
         </is>
@@ -2481,7 +2493,7 @@
       <c r="F57" s="38" t="n">
         <v>17000</v>
       </c>
-      <c r="G57" s="39" t="inlineStr">
+      <c r="G57" s="54" t="inlineStr">
         <is>
           <t>Thornfield-native account</t>
         </is>
@@ -2514,7 +2526,7 @@
       <c r="F58" s="32" t="n">
         <v>19800</v>
       </c>
-      <c r="G58" s="33" t="inlineStr">
+      <c r="G58" s="53" t="inlineStr">
         <is>
           <t>Thornfield-native account; regulated client</t>
         </is>
@@ -2547,7 +2559,7 @@
       <c r="F59" s="38" t="n">
         <v>34000</v>
       </c>
-      <c r="G59" s="39" t="inlineStr">
+      <c r="G59" s="54" t="inlineStr">
         <is>
           <t>inherited account; regulated client</t>
         </is>
@@ -2580,7 +2592,7 @@
       <c r="F60" s="32" t="n">
         <v>14700</v>
       </c>
-      <c r="G60" s="33" t="inlineStr">
+      <c r="G60" s="53" t="inlineStr">
         <is>
           <t>inherited account</t>
         </is>
@@ -2613,7 +2625,7 @@
       <c r="F61" s="38" t="n">
         <v>38200</v>
       </c>
-      <c r="G61" s="39" t="inlineStr">
+      <c r="G61" s="54" t="inlineStr">
         <is>
           <t>inherited account; regulated client</t>
         </is>
